--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128828402</v>
+        <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>91893</v>
+        <v>92792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,44 +819,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Askerudsberget, Vrm</t>
+          <t>Ingmår, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397436</v>
+        <v>397487</v>
       </c>
       <c r="R3" t="n">
-        <v>6639542</v>
+        <v>6639530</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,27 +876,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:52</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fruktkroppar från fjolåret på högstubbe av asp</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,33 +890,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Jonatan Axelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Jonatan Axelsson, Rob Nil, Nils Zachmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128828402</t>
+          <t>https://artportalen.se/Sighting/137104521</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111919018</v>
+        <v>128828402</v>
       </c>
       <c r="B4" t="n">
-        <v>91966</v>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,28 +925,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -978,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397508</v>
+        <v>397436</v>
       </c>
       <c r="R4" t="n">
-        <v>6639553</v>
+        <v>6639542</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,12 +986,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från fjolåret på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,16 +1021,129 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Björk, Martin Eneling, Jonas Göransson, Johanna Klauss, Edvin Johansson , Amanda Evensen, Olavi Niemelä, Agnes Rengren, August Oljeqvist, Åsa Röstell, Kim Ohlsson , Daniel Hertz Wallin</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128828402</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111919018</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Askerudsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>397508</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6639553</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Björk, Martin Eneling, Jonas Göransson, Johanna Klauss, Edvin Johansson , Amanda Evensen, Olavi Niemelä, Agnes Rengren, August Oljeqvist, Åsa Röstell, Kim Ohlsson , Daniel Hertz Wallin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111919018</t>
         </is>
@@ -1048,6 +1154,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92792</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92802</v>
+        <v>92804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92804</v>
+        <v>92817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92819</v>
+        <v>92822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>137104521</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
